--- a/logs/after_analysing_features/after_analysing_features.xlsx
+++ b/logs/after_analysing_features/after_analysing_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/after_analysing_features/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_25DDD2B7D3105479BBB92F11595ED87656CE1E8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4153A59F-2DB7-4EF2-97B1-17E35F2FE015}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_25DDD2B7D3105479BBB92F11595ED87656CE1E8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6993F5D1-658F-4B1B-B228-601C3E1C9E46}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="213">
   <si>
     <t>date</t>
   </si>
@@ -667,13 +667,22 @@
   </si>
   <si>
     <t>04-15_10-34-04_multihead_3heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 10:02:24</t>
+  </si>
+  <si>
+    <t>04-15_10-02-24_multihead_2heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>04-15_10-02-24_multihead_3heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,16 +696,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -717,6 +738,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -730,15 +766,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -782,6 +818,46 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -796,7 +872,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46127.44392824074" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{2DFB45BF-0A3F-41BE-B237-D6DAE2D77540}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46128.562491898148" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{2DFB45BF-0A3F-41BE-B237-D6DAE2D77540}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -1066,7 +1142,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="48">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
   <r>
     <s v="14/04/2026 14:12:50"/>
     <s v="04-14_14-12-50_multihead_2heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
@@ -4811,11 +4887,167 @@
     <n v="1234.8211393660879"/>
     <n v="-2.514518636458531"/>
   </r>
+  <r>
+    <s v="15/04/2026 10:02:24"/>
+    <s v="04-15_10-02-24_multihead_2heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="0"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="1"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['wv', 'yr', 'ya', 'rarad'], 'output_dim': 3, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, -1, 1, 3, -1, 2, 1, -1]}]"/>
+    <x v="0"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <n v="1"/>
+    <x v="1"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="160"/>
+    <n v="40"/>
+    <n v="120"/>
+    <n v="7.2382396935924201E-2"/>
+    <n v="11.576718933382001"/>
+    <n v="0.89874786407301777"/>
+    <n v="-1.96061842302239"/>
+    <n v="19.72334743392414"/>
+    <n v="0.87130856040929272"/>
+    <n v="19.72334743392414"/>
+    <n v="19.72334743392414"/>
+    <n v="0.87130856040929272"/>
+    <n v="111.43804872282981"/>
+    <n v="-0.96472278794951816"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="6.4075544807605999E-3"/>
+    <n v="0.95347286976741863"/>
+    <n v="6.4075544807605999E-3"/>
+    <n v="6.4075544807605999E-3"/>
+    <n v="0.95347286976741863"/>
+    <n v="0.78519784314463548"/>
+    <n v="-4.7015515694835894"/>
+    <n v="3.1740724776859103E-2"/>
+    <n v="0.89002516789600583"/>
+    <n v="3.1740724776859103E-2"/>
+    <n v="3.1740724776859103E-2"/>
+    <n v="0.89002516789600583"/>
+    <n v="0.13038188023579689"/>
+    <n v="0.54825463220711979"/>
+    <n v="3.3358249814488802E-2"/>
+    <n v="0.86607717827278574"/>
+    <n v="3.3358249814488802E-2"/>
+    <n v="3.3358249814488802E-2"/>
+    <n v="0.86607717827278574"/>
+    <n v="0.1095534875793172"/>
+    <n v="0.56017739934584454"/>
+    <n v="78.821883206624037"/>
+    <n v="0.77565902570096079"/>
+    <n v="78.821883206624037"/>
+    <n v="78.821883206624037"/>
+    <n v="0.77565902570096079"/>
+    <n v="444.72706168035847"/>
+    <n v="-0.26577161386745479"/>
+  </r>
+  <r>
+    <s v="15/04/2026 10:02:24"/>
+    <s v="04-15_10-02-24_multihead_3heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="3"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['wv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <n v="1"/>
+    <x v="3"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="160"/>
+    <n v="40"/>
+    <n v="120"/>
+    <n v="8.2812164625147303E-2"/>
+    <n v="3.9394210503660019"/>
+    <n v="0.89422988907591294"/>
+    <n v="-3.0305370577717179"/>
+    <n v="4.7485251394023216"/>
+    <n v="0.89403648567464455"/>
+    <n v="4.7485251394023216"/>
+    <n v="4.7485251394023216"/>
+    <n v="0.89403648567464455"/>
+    <n v="421.34812230940469"/>
+    <n v="-1.8895744946075901"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="8.0144114124647003E-3"/>
+    <n v="0.94180501084386115"/>
+    <n v="8.0144114124647003E-3"/>
+    <n v="8.0144114124647003E-3"/>
+    <n v="0.94180501084386115"/>
+    <n v="0.79168744914919886"/>
+    <n v="-4.748674499868196"/>
+    <n v="2.8530352739943001E-2"/>
+    <n v="0.90114842132620521"/>
+    <n v="2.8530352739943001E-2"/>
+    <n v="2.8530352739943001E-2"/>
+    <n v="0.90114842132620521"/>
+    <n v="0.16842877923992799"/>
+    <n v="0.41643025329100081"/>
+    <n v="5.3055723890813901E-2"/>
+    <n v="0.78699805020491143"/>
+    <n v="5.3055723890813901E-2"/>
+    <n v="5.3055723890813901E-2"/>
+    <n v="0.78699805020491143"/>
+    <n v="0.10764699836238251"/>
+    <n v="0.56783135052566625"/>
+    <n v="18.904500069566101"/>
+    <n v="0.94619446032359822"/>
+    <n v="18.904500069566101"/>
+    <n v="18.904500069566101"/>
+    <n v="0.94619446032359822"/>
+    <n v="1684.3247260108701"/>
+    <n v="-3.7938850823788242"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9096C394-E2A9-4483-A1AA-685A07651176}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9096C394-E2A9-4483-A1AA-685A07651176}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:L12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="76">
     <pivotField showAll="0"/>
@@ -4841,12 +5073,12 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="1"/>
+        <item t="default" sd="0"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
@@ -4874,8 +5106,8 @@
       <items count="6">
         <item sd="0" x="3"/>
         <item sd="0" x="2"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
+        <item x="1"/>
+        <item x="0"/>
         <item sd="0" x="4"/>
         <item t="default" sd="0"/>
       </items>
@@ -4936,13 +5168,22 @@
   </pivotFields>
   <rowFields count="4">
     <field x="17"/>
+    <field x="7"/>
     <field x="22"/>
-    <field x="7"/>
     <field x="2"/>
   </rowFields>
   <rowItems count="9">
     <i>
       <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
     </i>
     <i r="1">
       <x v="2"/>
@@ -4951,19 +5192,10 @@
       <x v="3"/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
+      <x v="2"/>
     </i>
     <i r="1">
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -5020,6 +5252,38 @@
     <dataField name="Promedio de Yaw Rate Global closed R2" fld="68" subtotal="average" baseField="22" baseItem="0"/>
     <dataField name="Promedio de Yaw Angle Global closed R2" fld="75" subtotal="average" baseField="22" baseItem="0"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="7" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="7" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5033,8 +5297,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}" name="Tabla1" displayName="Tabla1" ref="A1:BX49" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:BX49" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}" name="Tabla1" displayName="Tabla1" ref="A1:BX51" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:BX51" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="76">
     <tableColumn id="1" xr3:uid="{79DFB838-DDA6-48FC-9B9E-B5EA9B1C9BC7}" name="date"/>
     <tableColumn id="2" xr3:uid="{9247EBA5-E301-483F-B439-86EBE486B724}" name="model_id"/>
@@ -5402,7 +5672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX49"/>
+  <dimension ref="A1:BX51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
@@ -5928,7 +6198,7 @@
         <v>-0.1447300736262804</v>
       </c>
     </row>
-    <row r="3" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -6155,7 +6425,7 @@
         <v>-0.62745721990599157</v>
       </c>
     </row>
-    <row r="4" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -6382,7 +6652,7 @@
         <v>-0.30369947610391113</v>
       </c>
     </row>
-    <row r="5" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -6609,7 +6879,7 @@
         <v>-0.3337611535600471</v>
       </c>
     </row>
-    <row r="6" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -6836,7 +7106,7 @@
         <v>-0.36958798551333011</v>
       </c>
     </row>
-    <row r="7" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -7063,7 +7333,7 @@
         <v>-0.37387188648791692</v>
       </c>
     </row>
-    <row r="8" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>107</v>
       </c>
@@ -7290,7 +7560,7 @@
         <v>-0.41391951974648439</v>
       </c>
     </row>
-    <row r="9" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -7517,7 +7787,7 @@
         <v>-0.51665353697751004</v>
       </c>
     </row>
-    <row r="10" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -7744,7 +8014,7 @@
         <v>-0.20841395296405871</v>
       </c>
     </row>
-    <row r="11" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -7971,7 +8241,7 @@
         <v>-0.2242540164766047</v>
       </c>
     </row>
-    <row r="12" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>115</v>
       </c>
@@ -8198,7 +8468,7 @@
         <v>-0.68330047073975897</v>
       </c>
     </row>
-    <row r="13" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>117</v>
       </c>
@@ -8425,7 +8695,7 @@
         <v>-0.67613187020773657</v>
       </c>
     </row>
-    <row r="14" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>119</v>
       </c>
@@ -8652,7 +8922,7 @@
         <v>-0.5949224471054968</v>
       </c>
     </row>
-    <row r="15" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>121</v>
       </c>
@@ -8879,7 +9149,7 @@
         <v>-0.59295900948778768</v>
       </c>
     </row>
-    <row r="16" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -9106,7 +9376,7 @@
         <v>-0.23015331545736109</v>
       </c>
     </row>
-    <row r="17" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -9333,7 +9603,7 @@
         <v>-0.25428462364478688</v>
       </c>
     </row>
-    <row r="18" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -9560,7 +9830,7 @@
         <v>-7.5860908924296006E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -10014,7 +10284,7 @@
         <v>-3.7872417210927152</v>
       </c>
     </row>
-    <row r="21" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>135</v>
       </c>
@@ -10241,7 +10511,7 @@
         <v>-3.5117111486106638</v>
       </c>
     </row>
-    <row r="22" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>140</v>
       </c>
@@ -10468,7 +10738,7 @@
         <v>-2.5897216656214002</v>
       </c>
     </row>
-    <row r="23" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>142</v>
       </c>
@@ -10695,7 +10965,7 @@
         <v>-2.5946027111452921</v>
       </c>
     </row>
-    <row r="24" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>144</v>
       </c>
@@ -10922,7 +11192,7 @@
         <v>-0.26775049830371639</v>
       </c>
     </row>
-    <row r="25" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -11149,7 +11419,7 @@
         <v>-0.2624476587023809</v>
       </c>
     </row>
-    <row r="26" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>148</v>
       </c>
@@ -11376,7 +11646,7 @@
         <v>-0.96411522322623355</v>
       </c>
     </row>
-    <row r="27" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>150</v>
       </c>
@@ -11603,7 +11873,7 @@
         <v>-0.95884824025794435</v>
       </c>
     </row>
-    <row r="28" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>152</v>
       </c>
@@ -11830,7 +12100,7 @@
         <v>-3.6798927679978108</v>
       </c>
     </row>
-    <row r="29" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>154</v>
       </c>
@@ -12057,7 +12327,7 @@
         <v>-3.6377146535383509</v>
       </c>
     </row>
-    <row r="30" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>156</v>
       </c>
@@ -12284,7 +12554,7 @@
         <v>-0.66953354611017146</v>
       </c>
     </row>
-    <row r="31" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>158</v>
       </c>
@@ -12511,7 +12781,7 @@
         <v>-1.0679324579078531</v>
       </c>
     </row>
-    <row r="32" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>160</v>
       </c>
@@ -12738,7 +13008,7 @@
         <v>-3.244324430210209</v>
       </c>
     </row>
-    <row r="33" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>162</v>
       </c>
@@ -12965,7 +13235,7 @@
         <v>-3.4674599750727042</v>
       </c>
     </row>
-    <row r="34" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>164</v>
       </c>
@@ -13192,7 +13462,7 @@
         <v>-1.8050718450591119</v>
       </c>
     </row>
-    <row r="35" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -13419,7 +13689,7 @@
         <v>-1.769512188501712</v>
       </c>
     </row>
-    <row r="36" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>168</v>
       </c>
@@ -13646,7 +13916,7 @@
         <v>-3.5960412350740358</v>
       </c>
     </row>
-    <row r="37" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>170</v>
       </c>
@@ -14100,7 +14370,7 @@
         <v>-1.168090560192766</v>
       </c>
     </row>
-    <row r="39" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>176</v>
       </c>
@@ -14327,7 +14597,7 @@
         <v>-3.3597735486027358</v>
       </c>
     </row>
-    <row r="40" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>178</v>
       </c>
@@ -14554,7 +14824,7 @@
         <v>-1.6837549707824979</v>
       </c>
     </row>
-    <row r="41" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>180</v>
       </c>
@@ -14781,7 +15051,7 @@
         <v>-3.7296965152044361</v>
       </c>
     </row>
-    <row r="42" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>182</v>
       </c>
@@ -15008,7 +15278,7 @@
         <v>-5.0075000690213418</v>
       </c>
     </row>
-    <row r="43" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>184</v>
       </c>
@@ -15235,7 +15505,7 @@
         <v>-2.62220430816441</v>
       </c>
     </row>
-    <row r="44" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -15462,7 +15732,7 @@
         <v>-3.4318312286244388</v>
       </c>
     </row>
-    <row r="45" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>188</v>
       </c>
@@ -15689,7 +15959,7 @@
         <v>-1.780004782839816</v>
       </c>
     </row>
-    <row r="46" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>190</v>
       </c>
@@ -15916,7 +16186,7 @@
         <v>-1.1404208730468059</v>
       </c>
     </row>
-    <row r="47" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>192</v>
       </c>
@@ -16143,7 +16413,7 @@
         <v>-3.435863320429013</v>
       </c>
     </row>
-    <row r="48" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>207</v>
       </c>
@@ -16370,7 +16640,7 @@
         <v>-0.59719465190791077</v>
       </c>
     </row>
-    <row r="49" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:76" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>207</v>
       </c>
@@ -16595,6 +16865,460 @@
       </c>
       <c r="BX49">
         <v>-2.514518636458531</v>
+      </c>
+    </row>
+    <row r="50" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>210</v>
+      </c>
+      <c r="B50" t="s">
+        <v>211</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" t="s">
+        <v>79</v>
+      </c>
+      <c r="F50">
+        <v>16590</v>
+      </c>
+      <c r="G50">
+        <v>4.5</v>
+      </c>
+      <c r="H50" t="s">
+        <v>95</v>
+      </c>
+      <c r="I50" t="s">
+        <v>81</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50">
+        <v>5</v>
+      </c>
+      <c r="L50" t="s">
+        <v>82</v>
+      </c>
+      <c r="M50" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>96</v>
+      </c>
+      <c r="R50">
+        <v>2</v>
+      </c>
+      <c r="S50" t="s">
+        <v>85</v>
+      </c>
+      <c r="T50" t="s">
+        <v>86</v>
+      </c>
+      <c r="U50" t="s">
+        <v>87</v>
+      </c>
+      <c r="V50">
+        <v>1</v>
+      </c>
+      <c r="W50" t="s">
+        <v>97</v>
+      </c>
+      <c r="X50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z50">
+        <v>4000</v>
+      </c>
+      <c r="AA50">
+        <v>4000</v>
+      </c>
+      <c r="AC50">
+        <v>256</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE50">
+        <v>0.15</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG50">
+        <v>160</v>
+      </c>
+      <c r="AH50">
+        <v>40</v>
+      </c>
+      <c r="AI50">
+        <v>120</v>
+      </c>
+      <c r="AJ50">
+        <v>7.2382396935924201E-2</v>
+      </c>
+      <c r="AK50">
+        <v>11.576718933382001</v>
+      </c>
+      <c r="AL50">
+        <v>0.89874786407301777</v>
+      </c>
+      <c r="AM50">
+        <v>-1.96061842302239</v>
+      </c>
+      <c r="AN50">
+        <v>19.72334743392414</v>
+      </c>
+      <c r="AO50">
+        <v>0.87130856040929272</v>
+      </c>
+      <c r="AP50">
+        <v>19.72334743392414</v>
+      </c>
+      <c r="AQ50">
+        <v>19.72334743392414</v>
+      </c>
+      <c r="AR50">
+        <v>0.87130856040929272</v>
+      </c>
+      <c r="AS50">
+        <v>111.43804872282981</v>
+      </c>
+      <c r="AT50">
+        <v>-0.96472278794951816</v>
+      </c>
+      <c r="AU50">
+        <v>0.8</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW50">
+        <v>6.4075544807605999E-3</v>
+      </c>
+      <c r="AX50">
+        <v>0.95347286976741863</v>
+      </c>
+      <c r="AY50">
+        <v>6.4075544807605999E-3</v>
+      </c>
+      <c r="AZ50">
+        <v>6.4075544807605999E-3</v>
+      </c>
+      <c r="BA50">
+        <v>0.95347286976741863</v>
+      </c>
+      <c r="BB50">
+        <v>0.78519784314463548</v>
+      </c>
+      <c r="BC50">
+        <v>-4.7015515694835894</v>
+      </c>
+      <c r="BD50">
+        <v>3.1740724776859103E-2</v>
+      </c>
+      <c r="BE50">
+        <v>0.89002516789600583</v>
+      </c>
+      <c r="BF50">
+        <v>3.1740724776859103E-2</v>
+      </c>
+      <c r="BG50">
+        <v>3.1740724776859103E-2</v>
+      </c>
+      <c r="BH50">
+        <v>0.89002516789600583</v>
+      </c>
+      <c r="BI50">
+        <v>0.13038188023579689</v>
+      </c>
+      <c r="BJ50">
+        <v>0.54825463220711979</v>
+      </c>
+      <c r="BK50">
+        <v>3.3358249814488802E-2</v>
+      </c>
+      <c r="BL50">
+        <v>0.86607717827278574</v>
+      </c>
+      <c r="BM50">
+        <v>3.3358249814488802E-2</v>
+      </c>
+      <c r="BN50">
+        <v>3.3358249814488802E-2</v>
+      </c>
+      <c r="BO50">
+        <v>0.86607717827278574</v>
+      </c>
+      <c r="BP50">
+        <v>0.1095534875793172</v>
+      </c>
+      <c r="BQ50">
+        <v>0.56017739934584454</v>
+      </c>
+      <c r="BR50">
+        <v>78.821883206624037</v>
+      </c>
+      <c r="BS50">
+        <v>0.77565902570096079</v>
+      </c>
+      <c r="BT50">
+        <v>78.821883206624037</v>
+      </c>
+      <c r="BU50">
+        <v>78.821883206624037</v>
+      </c>
+      <c r="BV50">
+        <v>0.77565902570096079</v>
+      </c>
+      <c r="BW50">
+        <v>444.72706168035847</v>
+      </c>
+      <c r="BX50">
+        <v>-0.26577161386745479</v>
+      </c>
+    </row>
+    <row r="51" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>210</v>
+      </c>
+      <c r="B51" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51">
+        <v>16590</v>
+      </c>
+      <c r="G51">
+        <v>4.5</v>
+      </c>
+      <c r="H51" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" t="s">
+        <v>81</v>
+      </c>
+      <c r="J51">
+        <v>5</v>
+      </c>
+      <c r="K51">
+        <v>5</v>
+      </c>
+      <c r="L51" t="s">
+        <v>82</v>
+      </c>
+      <c r="M51" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>138</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
+      </c>
+      <c r="S51" t="s">
+        <v>85</v>
+      </c>
+      <c r="T51" t="s">
+        <v>86</v>
+      </c>
+      <c r="U51" t="s">
+        <v>87</v>
+      </c>
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51" t="s">
+        <v>139</v>
+      </c>
+      <c r="X51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z51">
+        <v>4000</v>
+      </c>
+      <c r="AA51">
+        <v>4000</v>
+      </c>
+      <c r="AC51">
+        <v>256</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE51">
+        <v>0.15</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG51">
+        <v>160</v>
+      </c>
+      <c r="AH51">
+        <v>40</v>
+      </c>
+      <c r="AI51">
+        <v>120</v>
+      </c>
+      <c r="AJ51">
+        <v>8.2812164625147303E-2</v>
+      </c>
+      <c r="AK51">
+        <v>3.9394210503660019</v>
+      </c>
+      <c r="AL51">
+        <v>0.89422988907591294</v>
+      </c>
+      <c r="AM51">
+        <v>-3.0305370577717179</v>
+      </c>
+      <c r="AN51">
+        <v>4.7485251394023216</v>
+      </c>
+      <c r="AO51">
+        <v>0.89403648567464455</v>
+      </c>
+      <c r="AP51">
+        <v>4.7485251394023216</v>
+      </c>
+      <c r="AQ51">
+        <v>4.7485251394023216</v>
+      </c>
+      <c r="AR51">
+        <v>0.89403648567464455</v>
+      </c>
+      <c r="AS51">
+        <v>421.34812230940469</v>
+      </c>
+      <c r="AT51">
+        <v>-1.8895744946075901</v>
+      </c>
+      <c r="AU51">
+        <v>0.8</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW51">
+        <v>8.0144114124647003E-3</v>
+      </c>
+      <c r="AX51">
+        <v>0.94180501084386115</v>
+      </c>
+      <c r="AY51">
+        <v>8.0144114124647003E-3</v>
+      </c>
+      <c r="AZ51">
+        <v>8.0144114124647003E-3</v>
+      </c>
+      <c r="BA51">
+        <v>0.94180501084386115</v>
+      </c>
+      <c r="BB51">
+        <v>0.79168744914919886</v>
+      </c>
+      <c r="BC51">
+        <v>-4.748674499868196</v>
+      </c>
+      <c r="BD51">
+        <v>2.8530352739943001E-2</v>
+      </c>
+      <c r="BE51">
+        <v>0.90114842132620521</v>
+      </c>
+      <c r="BF51">
+        <v>2.8530352739943001E-2</v>
+      </c>
+      <c r="BG51">
+        <v>2.8530352739943001E-2</v>
+      </c>
+      <c r="BH51">
+        <v>0.90114842132620521</v>
+      </c>
+      <c r="BI51">
+        <v>0.16842877923992799</v>
+      </c>
+      <c r="BJ51">
+        <v>0.41643025329100081</v>
+      </c>
+      <c r="BK51">
+        <v>5.3055723890813901E-2</v>
+      </c>
+      <c r="BL51">
+        <v>0.78699805020491143</v>
+      </c>
+      <c r="BM51">
+        <v>5.3055723890813901E-2</v>
+      </c>
+      <c r="BN51">
+        <v>5.3055723890813901E-2</v>
+      </c>
+      <c r="BO51">
+        <v>0.78699805020491143</v>
+      </c>
+      <c r="BP51">
+        <v>0.10764699836238251</v>
+      </c>
+      <c r="BQ51">
+        <v>0.56783135052566625</v>
+      </c>
+      <c r="BR51">
+        <v>18.904500069566101</v>
+      </c>
+      <c r="BS51">
+        <v>0.94619446032359822</v>
+      </c>
+      <c r="BT51">
+        <v>18.904500069566101</v>
+      </c>
+      <c r="BU51">
+        <v>18.904500069566101</v>
+      </c>
+      <c r="BV51">
+        <v>0.94619446032359822</v>
+      </c>
+      <c r="BW51">
+        <v>1684.3247260108701</v>
+      </c>
+      <c r="BX51">
+        <v>-3.7938850823788242</v>
       </c>
     </row>
   </sheetData>
@@ -16610,18 +17334,18 @@
   <dimension ref="A3:L12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -16666,303 +17390,303 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.87950297813329237</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.94189970045124016</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.8934117257290376</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0.87549857966474431</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.80720190668814618</v>
-      </c>
-      <c r="H4" s="4">
-        <v>-0.90147416900562027</v>
-      </c>
-      <c r="I4" s="4">
-        <v>-3.3279101404412201</v>
-      </c>
-      <c r="J4" s="4">
-        <v>7.9369920578218053E-2</v>
-      </c>
-      <c r="K4" s="4">
-        <v>3.0301128420930305E-2</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-0.38765758458041377</v>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>0.87909325724709242</v>
+      </c>
+      <c r="D4">
+        <v>0.94247835891704912</v>
+      </c>
+      <c r="E4">
+        <v>0.89324239783738579</v>
+      </c>
+      <c r="F4">
+        <v>0.87502750959514641</v>
+      </c>
+      <c r="G4">
+        <v>0.80562476263878702</v>
+      </c>
+      <c r="H4">
+        <v>-0.9046365999528152</v>
+      </c>
+      <c r="I4">
+        <v>-3.3965922118933385</v>
+      </c>
+      <c r="J4">
+        <v>0.10281415615966313</v>
+      </c>
+      <c r="K4">
+        <v>5.6794941967176008E-2</v>
+      </c>
+      <c r="L4">
+        <v>-0.38156328604476586</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="4">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.88007410395023455</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.94126098585880036</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.89360623049995247</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.87625021982136064</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.80917897962082375</v>
-      </c>
-      <c r="H5" s="4">
-        <v>-0.8933021963741048</v>
-      </c>
-      <c r="I5" s="4">
-        <v>-3.2492438889917898</v>
-      </c>
-      <c r="J5" s="4">
-        <v>6.1572251139110384E-2</v>
-      </c>
-      <c r="K5" s="4">
-        <v>4.1645519629982903E-3</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-0.38970169960674317</v>
+      <c r="A5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>0.87898896489804434</v>
+      </c>
+      <c r="D5">
+        <v>0.94247454358443628</v>
+      </c>
+      <c r="E5">
+        <v>0.89323667143521379</v>
+      </c>
+      <c r="F5">
+        <v>0.87482210352378975</v>
+      </c>
+      <c r="G5">
+        <v>0.80542254104873623</v>
+      </c>
+      <c r="H5">
+        <v>-0.90882894437398409</v>
+      </c>
+      <c r="I5">
+        <v>-3.3987097667457071</v>
+      </c>
+      <c r="J5">
+        <v>9.5387823073414965E-2</v>
+      </c>
+      <c r="K5">
+        <v>5.3824047233069106E-2</v>
+      </c>
+      <c r="L5">
+        <v>-0.38581788105671738</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="C6" s="4">
-        <v>0.87898896489804434</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.94247454358443628</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.89323667143521379</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.87482210352378975</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.80542254104873623</v>
-      </c>
-      <c r="H6" s="4">
-        <v>-0.90882894437398409</v>
-      </c>
-      <c r="I6" s="4">
-        <v>-3.3987097667457071</v>
-      </c>
-      <c r="J6" s="4">
-        <v>9.5387823073414965E-2</v>
-      </c>
-      <c r="K6" s="4">
-        <v>5.3824047233069106E-2</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-0.38581788105671738</v>
+      <c r="C6">
+        <v>0.87919754959614038</v>
+      </c>
+      <c r="D6">
+        <v>0.94248217424966219</v>
+      </c>
+      <c r="E6">
+        <v>0.89324812423955779</v>
+      </c>
+      <c r="F6">
+        <v>0.8752329156665033</v>
+      </c>
+      <c r="G6">
+        <v>0.80582698422883747</v>
+      </c>
+      <c r="H6">
+        <v>-0.9004442555316462</v>
+      </c>
+      <c r="I6">
+        <v>-3.3944746570409698</v>
+      </c>
+      <c r="J6">
+        <v>0.11024048924591132</v>
+      </c>
+      <c r="K6">
+        <v>5.9765836701282916E-2</v>
+      </c>
+      <c r="L6">
+        <v>-0.37730869103281434</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="4">
-        <v>19</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.90727354127812965</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.93526761818861848</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.90598428329450298</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0.86325238206170385</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.92458988156769206</v>
-      </c>
-      <c r="H7" s="4">
-        <v>-1.1601558091261277</v>
-      </c>
-      <c r="I7" s="4">
-        <v>-2.8068332603608943</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0.2179793441160606</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0.26366196378979362</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-2.3154312840494717</v>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>0.90661168849795537</v>
+      </c>
+      <c r="D7">
+        <v>0.93559448782138088</v>
+      </c>
+      <c r="E7">
+        <v>0.90574249019608799</v>
+      </c>
+      <c r="F7">
+        <v>0.8594396654688643</v>
+      </c>
+      <c r="G7">
+        <v>0.92567011050548742</v>
+      </c>
+      <c r="H7">
+        <v>-1.1966267434002007</v>
+      </c>
+      <c r="I7">
+        <v>-2.9039253223362591</v>
+      </c>
+      <c r="J7">
+        <v>0.22790188957480764</v>
+      </c>
+      <c r="K7">
+        <v>0.27887043312658732</v>
+      </c>
+      <c r="L7">
+        <v>-2.3893539739659397</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="4">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.9079715122143962</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.93485542400808597</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.90631606559572775</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0.86717533339258324</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.92353922586118697</v>
-      </c>
-      <c r="H8" s="4">
-        <v>-1.1394202269873037</v>
-      </c>
-      <c r="I8" s="4">
-        <v>-2.7030579535676971</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0.21388394517641243</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0.2509356368627374</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-2.3194425364206697</v>
+      <c r="A8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>0.90664536743548985</v>
+      </c>
+      <c r="D8">
+        <v>0.93563859295109775</v>
+      </c>
+      <c r="E8">
+        <v>0.9056856792234006</v>
+      </c>
+      <c r="F8">
+        <v>0.85972172586391249</v>
+      </c>
+      <c r="G8">
+        <v>0.925535471703547</v>
+      </c>
+      <c r="H8">
+        <v>-1.178817833051069</v>
+      </c>
+      <c r="I8">
+        <v>-2.9002310364747705</v>
+      </c>
+      <c r="J8">
+        <v>0.22166520316174401</v>
+      </c>
+      <c r="K8">
+        <v>0.27511565802414428</v>
+      </c>
+      <c r="L8">
+        <v>-2.3118211569153937</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="A9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="C9" s="4">
-        <v>0.90664536743548985</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.93563859295109775</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.9056856792234006</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.85972172586391249</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.925535471703547</v>
-      </c>
-      <c r="H9" s="4">
-        <v>-1.178817833051069</v>
-      </c>
-      <c r="I9" s="4">
-        <v>-2.9002310364747705</v>
-      </c>
-      <c r="J9" s="4">
-        <v>0.22166520316174401</v>
-      </c>
-      <c r="K9" s="4">
-        <v>0.27511565802414428</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-2.3118211569153937</v>
+      <c r="C9">
+        <v>0.90657800956042112</v>
+      </c>
+      <c r="D9">
+        <v>0.93555038269166357</v>
+      </c>
+      <c r="E9">
+        <v>0.90579930116877549</v>
+      </c>
+      <c r="F9">
+        <v>0.859157605073816</v>
+      </c>
+      <c r="G9">
+        <v>0.92580474930742818</v>
+      </c>
+      <c r="H9">
+        <v>-1.2144356537493324</v>
+      </c>
+      <c r="I9">
+        <v>-2.9076196081977472</v>
+      </c>
+      <c r="J9">
+        <v>0.23413857598787127</v>
+      </c>
+      <c r="K9">
+        <v>0.28262520822903026</v>
+      </c>
+      <c r="L9">
+        <v>-2.4668867910164853</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>10</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10">
         <v>0.93436868131083983</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10">
         <v>0.94098523663345612</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10">
         <v>0.94340582890391711</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10">
         <v>0.92224098374634345</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10">
         <v>0.93084267595964243</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10">
         <v>-0.84635344168980498</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10">
         <v>-1.6587844510604088</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>0.13411707024764968</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>0.87516763174436285</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10">
         <v>-2.7359140176908263</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="4">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>0.93436868131083983</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11">
         <v>0.94098523663345612</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11">
         <v>0.94340582890391711</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11">
         <v>0.92224098374634345</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11">
         <v>0.93084267595964243</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11">
         <v>-0.84635344168980498</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11">
         <v>-1.6587844510604088</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11">
         <v>0.13411707024764968</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11">
         <v>0.87516763174436285</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11">
         <v>-2.7359140176908263</v>
       </c>
     </row>
@@ -16970,41 +17694,53 @@
       <c r="A12" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B12" s="4">
-        <v>48</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0.90192584754011274</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.93908398792691417</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.90880380126013416</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0.88038912729720742</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.87942647367619486</v>
-      </c>
-      <c r="H12" s="4">
-        <v>-0.9923855000291929</v>
-      </c>
-      <c r="I12" s="4">
-        <v>-2.7739160234550884</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0.14564180690974568</v>
-      </c>
-      <c r="K12" s="4">
-        <v>0.29868698061348714</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-1.6399547641849181</v>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>0.90115571456018728</v>
+      </c>
+      <c r="D12">
+        <v>0.93942618602206318</v>
+      </c>
+      <c r="E12">
+        <v>0.90827512099417329</v>
+      </c>
+      <c r="F12">
+        <v>0.87823506677487306</v>
+      </c>
+      <c r="G12">
+        <v>0.87868648444963826</v>
+      </c>
+      <c r="H12">
+        <v>-1.0097760256791675</v>
+      </c>
+      <c r="I12">
+        <v>-2.8519639039039202</v>
+      </c>
+      <c r="J12">
+        <v>0.15910983234331819</v>
+      </c>
+      <c r="K12">
+        <v>0.3092996763863779</v>
+      </c>
+      <c r="L12">
+        <v>-1.6555497075424472</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C3:L12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.85"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>